--- a/ref/progress.xlsx
+++ b/ref/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinaskominfo/kiken/Project/next/e-office2026/ref/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A804E67-B8A7-4144-B01F-0613D9F26E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AF45AF-6178-A948-A75F-99955B96C515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15300" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
+    <workbookView xWindow="6160" yWindow="1000" windowWidth="27640" windowHeight="15300" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -971,7 +971,7 @@
       </c>
     </row>
     <row r="18" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
     </row>
     <row r="21" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
     </row>
     <row r="68" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="6" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
     </row>
     <row r="85" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="6" t="s">
         <v>83</v>
       </c>
     </row>

--- a/ref/progress.xlsx
+++ b/ref/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinaskominfo/kiken/Project/next/e-office2026/ref/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AF45AF-6178-A948-A75F-99955B96C515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F6F5AF-5B7C-A641-B7B0-A022D4ABDA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="1000" windowWidth="27640" windowHeight="15300" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
   </bookViews>
@@ -1031,22 +1031,22 @@
       </c>
     </row>
     <row r="30" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1196,17 +1196,17 @@
       </c>
     </row>
     <row r="63" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
     </row>
     <row r="87" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="6" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
     </row>
     <row r="117" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="2" t="s">
         <v>114</v>
       </c>
     </row>

--- a/ref/progress.xlsx
+++ b/ref/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinaskominfo/kiken/Project/next/e-office2026/ref/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F6F5AF-5B7C-A641-B7B0-A022D4ABDA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054CD756-FA39-9F47-B581-D468B9EC2E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6160" yWindow="1000" windowWidth="27640" windowHeight="15300" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -921,12 +921,12 @@
       </c>
     </row>
     <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1086,22 +1086,22 @@
       </c>
     </row>
     <row r="41" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
     </row>
     <row r="66" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="5" t="s">
         <v>64</v>
       </c>
     </row>

--- a/ref/progress.xlsx
+++ b/ref/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinaskominfo/kiken/Project/next/e-office2026/ref/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054CD756-FA39-9F47-B581-D468B9EC2E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262B2E83-9AF1-A14E-81D1-0082AC0E394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{B48B6E4E-04F9-0B46-B445-3CEA96597E01}"/>
   </bookViews>
@@ -480,7 +480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -535,6 +535,13 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -556,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -565,6 +572,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1106,12 +1114,12 @@
       </c>
     </row>
     <row r="45" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1421,17 +1429,17 @@
       </c>
     </row>
     <row r="108" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="5" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1456,7 +1464,7 @@
       </c>
     </row>
     <row r="115" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1481,7 +1489,7 @@
       </c>
     </row>
     <row r="120" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="5" t="s">
         <v>117</v>
       </c>
     </row>
